--- a/7936.T.xlsx
+++ b/7936.T.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F869E951-9DD3-4030-AA9A-37E97678F34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6198E44-F0DE-40A5-8398-47429DE97136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{86C4971A-A7D1-48DA-A0F7-A80DD1620C15}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{86C4971A-A7D1-48DA-A0F7-A80DD1620C15}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>Oscar Settje</author>
   </authors>
   <commentList>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{2433AD1F-7026-4777-9395-9F162F3DAAE9}">
+    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{2433AD1F-7026-4777-9395-9F162F3DAAE9}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>Asics Group</t>
   </si>
@@ -267,6 +267,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Walking</t>
+  </si>
 </sst>
 </file>
 
@@ -277,13 +280,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -345,6 +354,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -365,31 +382,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -748,7 +770,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="3">
-        <v>4496</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -756,10 +778,10 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>708.70524699999999</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>61</v>
+        <v>708.79401900000005</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -771,7 +793,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>3186338.7905119997</v>
+        <v>3743141.2143390002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -782,10 +804,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>119389</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>61</v>
+        <v>112267</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -793,15 +815,15 @@
         <v>5</v>
       </c>
       <c r="I6" s="3">
-        <f>10000+40000+25000</f>
-        <v>75000</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>61</v>
+        <f>2500+10000+25000</f>
+        <v>37500</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="17" t="s">
         <v>48</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -809,7 +831,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>3141949.7905119997</v>
+        <v>3668374.2143390002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -842,7 +864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0781B03-897F-4FBF-8E19-27D8F6677ACE}">
-  <dimension ref="A1:BR318"/>
+  <dimension ref="A1:BR319"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1001,6 +1023,10 @@
       <c r="O6" s="8">
         <v>116743</v>
       </c>
+      <c r="P6" s="8">
+        <f>220652-O6</f>
+        <v>103909</v>
+      </c>
       <c r="X6" s="8">
         <v>285929</v>
       </c>
@@ -1028,7 +1054,7 @@
         <v>20618</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:F24" si="0">+X7-SUM(C7:E7)</f>
+        <f t="shared" ref="F7:F25" si="0">+X7-SUM(C7:E7)</f>
         <v>11106</v>
       </c>
       <c r="G7" s="8">
@@ -1043,7 +1069,7 @@
         <v>22798</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" ref="J7:J24" si="1">+Y7-SUM(G7:I7)</f>
+        <f t="shared" ref="J7:J25" si="1">+Y7-SUM(G7:I7)</f>
         <v>13736</v>
       </c>
       <c r="K7" s="8">
@@ -1063,6 +1089,10 @@
       </c>
       <c r="O7" s="8">
         <v>30551</v>
+      </c>
+      <c r="P7" s="8">
+        <f>55111-O7</f>
+        <v>24560</v>
       </c>
       <c r="X7" s="8">
         <v>72154</v>
@@ -1127,6 +1157,10 @@
       <c r="O8" s="8">
         <v>14426</v>
       </c>
+      <c r="P8" s="8">
+        <f>25629-O8</f>
+        <v>11203</v>
+      </c>
       <c r="X8" s="8">
         <v>36185</v>
       </c>
@@ -1190,6 +1224,10 @@
       <c r="O9" s="8">
         <v>59621</v>
       </c>
+      <c r="P9" s="8">
+        <f>123186-O9</f>
+        <v>63565</v>
+      </c>
       <c r="X9" s="8">
         <v>59257</v>
       </c>
@@ -1253,6 +1291,10 @@
       <c r="O10" s="8">
         <v>37891</v>
       </c>
+      <c r="P10" s="8">
+        <f>89533-O10</f>
+        <v>51642</v>
+      </c>
       <c r="X10" s="8">
         <v>60304</v>
       </c>
@@ -1265,1204 +1307,1208 @@
     </row>
     <row r="11" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="8">
+        <v>7882</v>
+      </c>
+      <c r="P11" s="8">
+        <v>8657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C12" s="11">
         <v>152297</v>
       </c>
-      <c r="D11" s="11">
-        <f>290079-C11</f>
+      <c r="D12" s="11">
+        <f>290079-C12</f>
         <v>137782</v>
       </c>
-      <c r="E11" s="11">
-        <f>448105-SUM(C11:D11)</f>
+      <c r="E12" s="11">
+        <f>448105-SUM(C12:D12)</f>
         <v>158026</v>
       </c>
-      <c r="F11" s="11">
-        <f>+X11-SUM(C11:E11)</f>
+      <c r="F12" s="11">
+        <f>+X12-SUM(C12:E12)</f>
         <v>122358</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G12" s="11">
         <v>174102</v>
       </c>
-      <c r="H11" s="11">
-        <f>342199-G11</f>
+      <c r="H12" s="11">
+        <f>342199-G12</f>
         <v>168097</v>
       </c>
-      <c r="I11" s="11">
-        <f>525454-SUM(G11:H11)</f>
+      <c r="I12" s="11">
+        <f>525454-SUM(G12:H12)</f>
         <v>183255</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J12" s="11">
         <f t="shared" si="1"/>
         <v>153072</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K12" s="11">
         <v>208313</v>
       </c>
-      <c r="L11" s="11">
-        <f>402798-K11</f>
+      <c r="L12" s="11">
+        <f>402798-K12</f>
         <v>194485</v>
       </c>
-      <c r="M11" s="11">
-        <f>625055-SUM(K11:L11)</f>
+      <c r="M12" s="11">
+        <f>625055-SUM(K12:L12)</f>
         <v>222257</v>
       </c>
-      <c r="N11" s="11">
-        <f>+Z11-SUM(K11:M11)</f>
+      <c r="N12" s="11">
+        <f>+Z12-SUM(K12:M12)</f>
         <v>185861</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O12" s="11">
         <v>270265</v>
       </c>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="V11" s="11">
+      <c r="P12" s="11">
+        <f>534483-O12</f>
+        <v>264218</v>
+      </c>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="V12" s="11">
         <v>404083</v>
       </c>
-      <c r="W11" s="11">
+      <c r="W12" s="11">
         <v>484601</v>
       </c>
-      <c r="X11" s="11">
+      <c r="X12" s="11">
         <v>570463</v>
       </c>
-      <c r="Y11" s="11">
+      <c r="Y12" s="11">
         <v>678526</v>
       </c>
-      <c r="Z11" s="11">
+      <c r="Z12" s="11">
         <v>810916</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="8">
-        <v>75873</v>
-      </c>
-      <c r="D12" s="8">
-        <v>142083</v>
-      </c>
-      <c r="E12" s="8">
-        <v>218477</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="0"/>
-        <v>-162867</v>
-      </c>
-      <c r="G12" s="8">
-        <v>79254</v>
-      </c>
-      <c r="H12" s="8">
-        <f>152108-G12</f>
-        <v>72854</v>
-      </c>
-      <c r="I12" s="8">
-        <f>234533-SUM(G12:H12)</f>
-        <v>82425</v>
-      </c>
-      <c r="J12" s="8">
-        <f t="shared" si="1"/>
-        <v>65115</v>
-      </c>
-      <c r="K12" s="8">
-        <v>91990</v>
-      </c>
-      <c r="L12" s="8">
-        <f>174356-K12</f>
-        <v>82366</v>
-      </c>
-      <c r="M12" s="8">
-        <f>271882-SUM(K12:L12)</f>
-        <v>97526</v>
-      </c>
-      <c r="N12" s="8">
-        <f>+Z12-SUM(K12:M12)</f>
-        <v>78401</v>
-      </c>
-      <c r="O12" s="8">
-        <v>122746</v>
-      </c>
-      <c r="V12" s="8">
-        <v>204205</v>
-      </c>
-      <c r="W12" s="8">
-        <v>243894</v>
-      </c>
-      <c r="X12" s="8">
-        <v>273566</v>
-      </c>
-      <c r="Y12" s="8">
-        <v>299648</v>
-      </c>
-      <c r="Z12" s="8">
-        <v>350283</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:H13" si="3">+C11-C12</f>
-        <v>76424</v>
+        <v>75873</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="3"/>
-        <v>-4301</v>
+        <v>142083</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="3"/>
-        <v>-60451</v>
+        <v>218477</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="3"/>
-        <v>285225</v>
+        <f t="shared" si="0"/>
+        <v>-162867</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="3"/>
-        <v>94848</v>
+        <v>79254</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="3"/>
-        <v>95243</v>
+        <f>152108-G13</f>
+        <v>72854</v>
       </c>
       <c r="I13" s="8">
-        <f>+I11-I12</f>
-        <v>100830</v>
+        <f>234533-SUM(G13:H13)</f>
+        <v>82425</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" ref="J13:O13" si="4">+J11-J12</f>
-        <v>87957</v>
+        <f t="shared" si="1"/>
+        <v>65115</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="4"/>
-        <v>116323</v>
+        <v>91990</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="4"/>
-        <v>112119</v>
+        <f>174356-K13</f>
+        <v>82366</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="4"/>
-        <v>124731</v>
+        <f>271882-SUM(K13:L13)</f>
+        <v>97526</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="4"/>
-        <v>107460</v>
+        <f>+Z13-SUM(K13:M13)</f>
+        <v>78401</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="4"/>
-        <v>147519</v>
+        <v>122746</v>
+      </c>
+      <c r="P13" s="8">
+        <f>228202-O13</f>
+        <v>105456</v>
       </c>
       <c r="V13" s="8">
-        <f>+V11-V12</f>
-        <v>199878</v>
+        <v>204205</v>
       </c>
       <c r="W13" s="8">
-        <f>+W11-W12</f>
-        <v>240707</v>
+        <v>243894</v>
       </c>
       <c r="X13" s="8">
-        <f>+X11-X12</f>
-        <v>296897</v>
+        <v>273566</v>
       </c>
       <c r="Y13" s="8">
-        <f>+Y11-Y12</f>
-        <v>378878</v>
+        <v>299648</v>
       </c>
       <c r="Z13" s="8">
-        <f>+Z11-Z12</f>
-        <v>460633</v>
+        <v>350283</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C14" s="8">
-        <v>54303</v>
+        <f t="shared" ref="C14:H14" si="3">+C12-C13</f>
+        <v>76424</v>
       </c>
       <c r="D14" s="8">
-        <v>114385</v>
+        <f t="shared" si="3"/>
+        <v>-4301</v>
       </c>
       <c r="E14" s="8">
-        <v>173822</v>
+        <f t="shared" si="3"/>
+        <v>-60451</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="0"/>
-        <v>-99830</v>
+        <f t="shared" si="3"/>
+        <v>285225</v>
       </c>
       <c r="G14" s="8">
-        <v>61034</v>
+        <f t="shared" si="3"/>
+        <v>94848</v>
       </c>
       <c r="H14" s="8">
-        <f>131094-G14</f>
-        <v>70060</v>
+        <f t="shared" si="3"/>
+        <v>95243</v>
       </c>
       <c r="I14" s="8">
-        <f>199397-SUM(G14:H14)</f>
-        <v>68303</v>
+        <f>+I12-I13</f>
+        <v>100830</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="1"/>
-        <v>79369</v>
+        <f t="shared" ref="J14:P14" si="4">+J12-J13</f>
+        <v>87957</v>
       </c>
       <c r="K14" s="8">
-        <v>71810</v>
+        <f t="shared" si="4"/>
+        <v>116323</v>
       </c>
       <c r="L14" s="8">
-        <f>147310-K14</f>
-        <v>75500</v>
+        <f t="shared" si="4"/>
+        <v>112119</v>
       </c>
       <c r="M14" s="8">
-        <f>225566-SUM(K14:L14)</f>
-        <v>78256</v>
+        <f t="shared" si="4"/>
+        <v>124731</v>
       </c>
       <c r="N14" s="8">
-        <f>+Z14-SUM(K14:M14)</f>
-        <v>92546</v>
+        <f t="shared" si="4"/>
+        <v>107460</v>
       </c>
       <c r="O14" s="8">
-        <v>86755</v>
+        <f t="shared" si="4"/>
+        <v>147519</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="4"/>
+        <v>158762</v>
       </c>
       <c r="V14" s="8">
-        <v>177932</v>
+        <f>+V12-V13</f>
+        <v>199878</v>
       </c>
       <c r="W14" s="8">
-        <v>206704</v>
+        <f>+W12-W13</f>
+        <v>240707</v>
       </c>
       <c r="X14" s="8">
-        <v>242680</v>
+        <f>+X12-X13</f>
+        <v>296897</v>
       </c>
       <c r="Y14" s="8">
-        <v>278766</v>
+        <f>+Y12-Y13</f>
+        <v>378878</v>
       </c>
       <c r="Z14" s="8">
-        <v>318112</v>
+        <f>+Z12-Z13</f>
+        <v>460633</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:H15" si="5">+C13-C14</f>
-        <v>22121</v>
+        <v>54303</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="5"/>
-        <v>-118686</v>
+        <v>114385</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="5"/>
-        <v>-234273</v>
+        <v>173822</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="5"/>
-        <v>385055</v>
+        <f t="shared" si="0"/>
+        <v>-99830</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="5"/>
-        <v>33814</v>
+        <v>61034</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="5"/>
-        <v>25183</v>
+        <f>131094-G15</f>
+        <v>70060</v>
       </c>
       <c r="I15" s="8">
-        <f>+I13-I14</f>
-        <v>32527</v>
+        <f>199397-SUM(G15:H15)</f>
+        <v>68303</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" ref="J15:O15" si="6">+J13-J14</f>
-        <v>8588</v>
+        <f t="shared" si="1"/>
+        <v>79369</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="6"/>
-        <v>44513</v>
+        <v>71810</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="6"/>
-        <v>36619</v>
+        <f>147310-K15</f>
+        <v>75500</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="6"/>
-        <v>46475</v>
+        <f>225566-SUM(K15:L15)</f>
+        <v>78256</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="6"/>
-        <v>14914</v>
+        <f>+Z15-SUM(K15:M15)</f>
+        <v>92546</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="6"/>
-        <v>60764</v>
+        <v>86755</v>
+      </c>
+      <c r="P15" s="8">
+        <f>185794-O15</f>
+        <v>99039</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15:W15" si="7">+V13-V14</f>
-        <v>21946</v>
+        <v>177932</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" si="7"/>
-        <v>34003</v>
+        <v>206704</v>
       </c>
       <c r="X15" s="8">
-        <f>+X13-X14</f>
-        <v>54217</v>
+        <v>242680</v>
       </c>
       <c r="Y15" s="8">
-        <f>+Y13-Y14</f>
-        <v>100112</v>
+        <v>278766</v>
       </c>
       <c r="Z15" s="8">
-        <f>+Z13-Z14</f>
-        <v>142521</v>
+        <v>318112</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="8">
-        <v>1511</v>
+        <f t="shared" ref="C16:H16" si="5">+C14-C15</f>
+        <v>22121</v>
       </c>
       <c r="D16" s="8">
-        <v>3482</v>
+        <f t="shared" si="5"/>
+        <v>-118686</v>
       </c>
       <c r="E16" s="8">
-        <v>4398</v>
+        <f t="shared" si="5"/>
+        <v>-234273</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="0"/>
-        <v>-4090</v>
+        <f t="shared" si="5"/>
+        <v>385055</v>
       </c>
       <c r="G16" s="8">
-        <v>1636</v>
+        <f t="shared" si="5"/>
+        <v>33814</v>
       </c>
       <c r="H16" s="8">
-        <f>3802-G16</f>
-        <v>2166</v>
+        <f t="shared" si="5"/>
+        <v>25183</v>
       </c>
       <c r="I16" s="8">
-        <f>5815-SUM(G16:H16)</f>
-        <v>2013</v>
+        <f>+I14-I15</f>
+        <v>32527</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="1"/>
-        <v>-70</v>
+        <f t="shared" ref="J16:P16" si="6">+J14-J15</f>
+        <v>8588</v>
       </c>
       <c r="K16" s="8">
-        <v>1640</v>
+        <f t="shared" si="6"/>
+        <v>44513</v>
       </c>
       <c r="L16" s="8">
-        <f>2551-K16</f>
-        <v>911</v>
+        <f t="shared" si="6"/>
+        <v>36619</v>
       </c>
       <c r="M16" s="8">
-        <f>3309-SUM(K16:L16)</f>
-        <v>758</v>
+        <f t="shared" si="6"/>
+        <v>46475</v>
       </c>
       <c r="N16" s="8">
-        <f>+Z16-SUM(K16:M16)</f>
-        <v>1271</v>
+        <f t="shared" si="6"/>
+        <v>14914</v>
       </c>
       <c r="O16" s="8">
-        <v>1023</v>
+        <f t="shared" si="6"/>
+        <v>60764</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="6"/>
+        <v>59723</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" ref="V16:W16" si="7">+V14-V15</f>
+        <v>21946</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" si="7"/>
+        <v>34003</v>
       </c>
       <c r="X16" s="8">
-        <v>5301</v>
+        <f>+X14-X15</f>
+        <v>54217</v>
       </c>
       <c r="Y16" s="8">
-        <v>5745</v>
+        <f>+Y14-Y15</f>
+        <v>100112</v>
       </c>
       <c r="Z16" s="8">
-        <v>4580</v>
+        <f>+Z14-Z15</f>
+        <v>142521</v>
       </c>
     </row>
     <row r="17" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="8">
-        <v>1711</v>
+        <v>1511</v>
       </c>
       <c r="D17" s="8">
-        <v>3273</v>
+        <v>3482</v>
       </c>
       <c r="E17" s="8">
-        <v>5455</v>
+        <v>4398</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="0"/>
-        <v>-1594</v>
+        <v>-4090</v>
       </c>
       <c r="G17" s="8">
-        <v>2372</v>
+        <v>1636</v>
       </c>
       <c r="H17" s="8">
-        <f>4976-G17</f>
-        <v>2604</v>
+        <f>3802-G17</f>
+        <v>2166</v>
       </c>
       <c r="I17" s="8">
-        <f>9059-SUM(G17:H17)</f>
-        <v>4083</v>
+        <f>5815-SUM(G17:H17)</f>
+        <v>2013</v>
       </c>
       <c r="J17" s="8">
         <f t="shared" si="1"/>
-        <v>4196</v>
+        <v>-70</v>
       </c>
       <c r="K17" s="8">
-        <v>2775</v>
+        <v>1640</v>
       </c>
       <c r="L17" s="8">
-        <f>5056-K17</f>
-        <v>2281</v>
+        <f>2551-K17</f>
+        <v>911</v>
       </c>
       <c r="M17" s="8">
-        <f>6415-SUM(K17:L17)</f>
-        <v>1359</v>
+        <f>3309-SUM(K17:L17)</f>
+        <v>758</v>
       </c>
       <c r="N17" s="8">
         <f>+Z17-SUM(K17:M17)</f>
-        <v>1389</v>
+        <v>1271</v>
       </c>
       <c r="O17" s="8">
-        <v>3011</v>
+        <v>1023</v>
+      </c>
+      <c r="P17" s="8">
+        <f>2357-O17</f>
+        <v>1334</v>
       </c>
       <c r="X17" s="8">
-        <v>8845</v>
+        <v>5301</v>
       </c>
       <c r="Y17" s="8">
-        <v>13255</v>
+        <v>5745</v>
       </c>
       <c r="Z17" s="8">
-        <v>7804</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="18" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:H18" si="8">+C15-C17+C16</f>
-        <v>21921</v>
+        <v>1711</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="8"/>
-        <v>-118477</v>
+        <v>3273</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="8"/>
-        <v>-235330</v>
+        <v>5455</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="8"/>
-        <v>382559</v>
+        <f t="shared" si="0"/>
+        <v>-1594</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="8"/>
-        <v>33078</v>
+        <v>2372</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="8"/>
-        <v>24745</v>
+        <f>4976-G18</f>
+        <v>2604</v>
       </c>
       <c r="I18" s="8">
-        <f>+I15-I17+I16</f>
-        <v>30457</v>
+        <f>9059-SUM(G18:H18)</f>
+        <v>4083</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" ref="J18:O18" si="9">+J15-J17+J16</f>
-        <v>4322</v>
+        <f t="shared" si="1"/>
+        <v>4196</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="9"/>
-        <v>43378</v>
+        <v>2775</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="9"/>
-        <v>35249</v>
+        <f>5056-K18</f>
+        <v>2281</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="9"/>
-        <v>45874</v>
+        <f>6415-SUM(K18:L18)</f>
+        <v>1359</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="9"/>
-        <v>14796</v>
+        <f>+Z18-SUM(K18:M18)</f>
+        <v>1389</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="9"/>
-        <v>58776</v>
+        <v>3011</v>
+      </c>
+      <c r="P18" s="8">
+        <f>6246-O18</f>
+        <v>3235</v>
       </c>
       <c r="X18" s="8">
-        <f>+X15+X16-X17</f>
-        <v>50673</v>
+        <v>8845</v>
       </c>
       <c r="Y18" s="8">
-        <f>+Y15+Y16-Y17</f>
-        <v>92602</v>
+        <v>13255</v>
       </c>
       <c r="Z18" s="8">
-        <f>+Z15+Z16-Z17</f>
-        <v>139297</v>
+        <v>7804</v>
       </c>
     </row>
     <row r="19" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C19" s="8">
-        <v>1</v>
+        <f t="shared" ref="C19:H19" si="8">+C16-C18+C17</f>
+        <v>21921</v>
       </c>
       <c r="D19" s="8">
-        <v>8</v>
+        <f t="shared" si="8"/>
+        <v>-118477</v>
       </c>
       <c r="E19" s="8">
-        <v>1499</v>
+        <f t="shared" si="8"/>
+        <v>-235330</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" si="0"/>
-        <v>6910</v>
+        <f t="shared" si="8"/>
+        <v>382559</v>
       </c>
       <c r="G19" s="8">
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>33078</v>
       </c>
       <c r="H19" s="8">
-        <f>267-G19</f>
-        <v>266</v>
+        <f t="shared" si="8"/>
+        <v>24745</v>
       </c>
       <c r="I19" s="8">
-        <f>5924-SUM(G19:H19)</f>
-        <v>5657</v>
+        <f>+I16-I18+I17</f>
+        <v>30457</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="1"/>
-        <v>1250</v>
+        <f t="shared" ref="J19:P19" si="9">+J16-J18+J17</f>
+        <v>4322</v>
       </c>
       <c r="K19" s="8">
-        <v>12</v>
+        <f t="shared" si="9"/>
+        <v>43378</v>
       </c>
       <c r="L19" s="8">
-        <f>2305-K19</f>
-        <v>2293</v>
+        <f t="shared" si="9"/>
+        <v>35249</v>
       </c>
       <c r="M19" s="8">
-        <f>2306-SUM(K19:L19)</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>45874</v>
       </c>
       <c r="N19" s="8">
-        <f>+Z19-SUM(K19:M19)</f>
-        <v>7</v>
+        <f t="shared" si="9"/>
+        <v>14796</v>
       </c>
       <c r="O19" s="8">
-        <v>3108</v>
+        <f t="shared" si="9"/>
+        <v>58776</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" si="9"/>
+        <v>57822</v>
       </c>
       <c r="X19" s="8">
-        <v>8418</v>
+        <f>+X16+X17-X18</f>
+        <v>50673</v>
       </c>
       <c r="Y19" s="8">
-        <v>7174</v>
+        <f>+Y16+Y17-Y18</f>
+        <v>92602</v>
       </c>
       <c r="Z19" s="8">
-        <v>2313</v>
+        <f>+Z16+Z17-Z18</f>
+        <v>139297</v>
       </c>
     </row>
     <row r="20" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="8">
-        <v>317</v>
+        <v>1</v>
       </c>
       <c r="D20" s="8">
-        <v>429</v>
+        <v>8</v>
       </c>
       <c r="E20" s="8">
-        <v>1019</v>
+        <v>1499</v>
       </c>
       <c r="F20" s="8">
         <f t="shared" si="0"/>
-        <v>6751</v>
+        <v>6910</v>
       </c>
       <c r="G20" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8">
-        <f>31-G20</f>
-        <v>16</v>
+        <f>267-G20</f>
+        <v>266</v>
       </c>
       <c r="I20" s="8">
-        <f>2129-SUM(G20:H20)</f>
-        <v>2098</v>
+        <f>5924-SUM(G20:H20)</f>
+        <v>5657</v>
       </c>
       <c r="J20" s="8">
         <f t="shared" si="1"/>
-        <v>4402</v>
+        <v>1250</v>
       </c>
       <c r="K20" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L20" s="8">
-        <f>200-K20</f>
-        <v>194</v>
+        <f>2305-K20</f>
+        <v>2293</v>
       </c>
       <c r="M20" s="8">
-        <f>268-SUM(K20:L20)</f>
-        <v>68</v>
+        <f>2306-SUM(K20:L20)</f>
+        <v>1</v>
       </c>
       <c r="N20" s="8">
         <f>+Z20-SUM(K20:M20)</f>
-        <v>2591</v>
+        <v>7</v>
       </c>
       <c r="O20" s="8">
-        <v>14</v>
+        <v>3108</v>
+      </c>
+      <c r="P20" s="8">
+        <f>3148-O20</f>
+        <v>40</v>
       </c>
       <c r="X20" s="8">
-        <v>8516</v>
+        <v>8418</v>
       </c>
       <c r="Y20" s="8">
-        <v>6531</v>
+        <v>7174</v>
       </c>
       <c r="Z20" s="8">
-        <v>2859</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="21" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:H21" si="10">+C18+C19-C20</f>
-        <v>21605</v>
+        <v>317</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="10"/>
-        <v>-118898</v>
+        <v>429</v>
       </c>
       <c r="E21" s="8">
-        <f t="shared" si="10"/>
-        <v>-234850</v>
+        <v>1019</v>
       </c>
       <c r="F21" s="8">
-        <f t="shared" si="10"/>
-        <v>382718</v>
+        <f t="shared" si="0"/>
+        <v>6751</v>
       </c>
       <c r="G21" s="8">
-        <f t="shared" si="10"/>
-        <v>33064</v>
+        <v>15</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" si="10"/>
-        <v>24995</v>
+        <f>31-G21</f>
+        <v>16</v>
       </c>
       <c r="I21" s="8">
-        <f>+I18+I19-I20</f>
-        <v>34016</v>
+        <f>2129-SUM(G21:H21)</f>
+        <v>2098</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" ref="J21:O21" si="11">+J18+J19-J20</f>
-        <v>1170</v>
+        <f t="shared" si="1"/>
+        <v>4402</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="11"/>
-        <v>43384</v>
+        <v>6</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="11"/>
-        <v>37348</v>
+        <f>200-K21</f>
+        <v>194</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="11"/>
-        <v>45807</v>
+        <f>268-SUM(K21:L21)</f>
+        <v>68</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="11"/>
-        <v>12212</v>
+        <f>+Z21-SUM(K21:M21)</f>
+        <v>2591</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="11"/>
-        <v>61870</v>
+        <v>14</v>
+      </c>
+      <c r="P21" s="8">
+        <f>8079-O21</f>
+        <v>8065</v>
       </c>
       <c r="X21" s="8">
-        <f>+X18+X19-X20</f>
-        <v>50575</v>
+        <v>8516</v>
       </c>
       <c r="Y21" s="8">
-        <f>+Y18+Y19-Y20</f>
-        <v>93245</v>
+        <v>6531</v>
       </c>
       <c r="Z21" s="8">
-        <f>+Z18+Z19-Z20</f>
-        <v>138751</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="22" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="8">
-        <v>5189</v>
+        <f t="shared" ref="C22:H22" si="10">+C19+C20-C21</f>
+        <v>21605</v>
       </c>
       <c r="D22" s="8">
-        <v>8473</v>
+        <f t="shared" si="10"/>
+        <v>-118898</v>
       </c>
       <c r="E22" s="8">
-        <v>14865</v>
+        <f t="shared" si="10"/>
+        <v>-234850</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="0"/>
-        <v>-13408</v>
+        <f t="shared" si="10"/>
+        <v>382718</v>
       </c>
       <c r="G22" s="8">
-        <v>6239</v>
+        <f t="shared" si="10"/>
+        <v>33064</v>
       </c>
       <c r="H22" s="8">
-        <f>15761-G22</f>
-        <v>9522</v>
+        <f t="shared" si="10"/>
+        <v>24995</v>
       </c>
       <c r="I22" s="8">
-        <f>27112-SUM(G22:H22)</f>
-        <v>11351</v>
+        <f>+I19+I20-I21</f>
+        <v>34016</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="1"/>
-        <v>2187</v>
+        <f t="shared" ref="J22:P22" si="11">+J19+J20-J21</f>
+        <v>1170</v>
       </c>
       <c r="K22" s="8">
-        <v>11654</v>
+        <f t="shared" si="11"/>
+        <v>43384</v>
       </c>
       <c r="L22" s="8">
-        <f>27048-K22</f>
-        <v>15394</v>
+        <f t="shared" si="11"/>
+        <v>37348</v>
       </c>
       <c r="M22" s="8">
-        <f>40166-SUM(K22:L22)</f>
-        <v>13118</v>
+        <f t="shared" si="11"/>
+        <v>45807</v>
       </c>
       <c r="N22" s="8">
-        <f>+Z22-SUM(K22:M22)</f>
-        <v>-246</v>
+        <f t="shared" si="11"/>
+        <v>12212</v>
       </c>
       <c r="O22" s="8">
-        <v>15198</v>
+        <f t="shared" si="11"/>
+        <v>61870</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="11"/>
+        <v>49797</v>
       </c>
       <c r="X22" s="8">
-        <v>15119</v>
+        <f>+X19+X20-X21</f>
+        <v>50575</v>
       </c>
       <c r="Y22" s="8">
-        <v>29299</v>
+        <f>+Y19+Y20-Y21</f>
+        <v>93245</v>
       </c>
       <c r="Z22" s="8">
-        <v>39920</v>
+        <f>+Z19+Z20-Z21</f>
+        <v>138751</v>
       </c>
     </row>
     <row r="23" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:H23" si="12">+C21-C22</f>
-        <v>16416</v>
+        <v>5189</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="12"/>
-        <v>-127371</v>
+        <v>8473</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="12"/>
-        <v>-249715</v>
+        <v>14865</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="12"/>
-        <v>396126</v>
+        <f t="shared" si="0"/>
+        <v>-13408</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" si="12"/>
-        <v>26825</v>
+        <v>6239</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="12"/>
-        <v>15473</v>
+        <f>15761-G23</f>
+        <v>9522</v>
       </c>
       <c r="I23" s="8">
-        <f>+I21-I22</f>
-        <v>22665</v>
+        <f>27112-SUM(G23:H23)</f>
+        <v>11351</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" ref="J23:O23" si="13">+J21-J22</f>
-        <v>-1017</v>
+        <f t="shared" si="1"/>
+        <v>2187</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="13"/>
-        <v>31730</v>
+        <v>11654</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="13"/>
-        <v>21954</v>
+        <f>27048-K23</f>
+        <v>15394</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="13"/>
-        <v>32689</v>
+        <f>40166-SUM(K23:L23)</f>
+        <v>13118</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="13"/>
-        <v>12458</v>
+        <f>+Z23-SUM(K23:M23)</f>
+        <v>-246</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" si="13"/>
-        <v>46672</v>
+        <v>15198</v>
+      </c>
+      <c r="P23" s="8">
+        <f>29397-O23</f>
+        <v>14199</v>
       </c>
       <c r="X23" s="8">
-        <f>+X21-X22</f>
-        <v>35456</v>
+        <v>15119</v>
       </c>
       <c r="Y23" s="8">
-        <f>+Y21-Y22</f>
-        <v>63946</v>
+        <v>29299</v>
       </c>
       <c r="Z23" s="8">
-        <f>+Z21-Z22</f>
-        <v>98831</v>
+        <v>39920</v>
       </c>
     </row>
     <row r="24" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="8">
-        <v>105</v>
+        <f t="shared" ref="C24:H24" si="12">+C22-C23</f>
+        <v>16416</v>
       </c>
       <c r="D24" s="8">
-        <v>129</v>
+        <f t="shared" si="12"/>
+        <v>-127371</v>
       </c>
       <c r="E24" s="8">
-        <v>81</v>
+        <f t="shared" si="12"/>
+        <v>-249715</v>
       </c>
       <c r="F24" s="8">
-        <f t="shared" si="0"/>
-        <v>-135</v>
+        <f t="shared" si="12"/>
+        <v>396126</v>
       </c>
       <c r="G24" s="8">
-        <v>85</v>
+        <f t="shared" si="12"/>
+        <v>26825</v>
       </c>
       <c r="H24" s="8">
-        <f>77-G24</f>
-        <v>-8</v>
+        <f t="shared" si="12"/>
+        <v>15473</v>
       </c>
       <c r="I24" s="8">
-        <f>20-SUM(G24:H24)</f>
-        <v>-57</v>
+        <f>+I22-I23</f>
+        <v>22665</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="1"/>
-        <v>118</v>
+        <f t="shared" ref="J24:P24" si="13">+J22-J23</f>
+        <v>-1017</v>
       </c>
       <c r="K24" s="8">
-        <v>80</v>
+        <f t="shared" si="13"/>
+        <v>31730</v>
       </c>
       <c r="L24" s="8">
-        <f>76-K24</f>
-        <v>-4</v>
+        <f t="shared" si="13"/>
+        <v>21954</v>
       </c>
       <c r="M24" s="8">
-        <f>56-SUM(K24:L24)</f>
-        <v>-20</v>
+        <f t="shared" si="13"/>
+        <v>32689</v>
       </c>
       <c r="N24" s="8">
-        <f>+Z24-SUM(K24:M24)</f>
-        <v>52</v>
+        <f t="shared" si="13"/>
+        <v>12458</v>
       </c>
       <c r="O24" s="8">
-        <v>101</v>
+        <f t="shared" si="13"/>
+        <v>46672</v>
+      </c>
+      <c r="P24" s="8">
+        <f t="shared" si="13"/>
+        <v>35598</v>
       </c>
       <c r="X24" s="8">
-        <v>180</v>
+        <f>+X22-X23</f>
+        <v>35456</v>
       </c>
       <c r="Y24" s="8">
-        <v>138</v>
+        <f>+Y22-Y23</f>
+        <v>63946</v>
       </c>
       <c r="Z24" s="8">
-        <v>108</v>
+        <f>+Z22-Z23</f>
+        <v>98831</v>
       </c>
     </row>
     <row r="25" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="8">
+        <v>105</v>
+      </c>
+      <c r="D25" s="8">
+        <v>129</v>
+      </c>
+      <c r="E25" s="8">
+        <v>81</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="0"/>
+        <v>-135</v>
+      </c>
+      <c r="G25" s="8">
+        <v>85</v>
+      </c>
+      <c r="H25" s="8">
+        <f>77-G25</f>
+        <v>-8</v>
+      </c>
+      <c r="I25" s="8">
+        <f>20-SUM(G25:H25)</f>
+        <v>-57</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="K25" s="8">
+        <v>80</v>
+      </c>
+      <c r="L25" s="8">
+        <f>76-K25</f>
+        <v>-4</v>
+      </c>
+      <c r="M25" s="8">
+        <f>56-SUM(K25:L25)</f>
+        <v>-20</v>
+      </c>
+      <c r="N25" s="8">
+        <f>+Z25-SUM(K25:M25)</f>
+        <v>52</v>
+      </c>
+      <c r="O25" s="8">
+        <v>101</v>
+      </c>
+      <c r="P25" s="8">
+        <f>97-O25</f>
+        <v>-4</v>
+      </c>
+      <c r="X25" s="8">
+        <v>180</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>138</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="8">
-        <f t="shared" ref="C25:H25" si="14">+C23-C24</f>
+      <c r="C26" s="8">
+        <f t="shared" ref="C26:H26" si="14">+C24-C25</f>
         <v>16311</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D26" s="8">
         <f t="shared" si="14"/>
         <v>-127500</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E26" s="8">
         <f t="shared" si="14"/>
         <v>-249796</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F26" s="8">
         <f t="shared" si="14"/>
         <v>396261</v>
       </c>
-      <c r="G25" s="8">
-        <f>+G23-G24</f>
+      <c r="G26" s="8">
+        <f>+G24-G25</f>
         <v>26740</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H26" s="8">
         <f t="shared" si="14"/>
         <v>15481</v>
       </c>
-      <c r="I25" s="8">
-        <f>+I23-I24</f>
+      <c r="I26" s="8">
+        <f>+I24-I25</f>
         <v>22722</v>
       </c>
-      <c r="J25" s="8">
-        <f t="shared" ref="J25:O25" si="15">+J23-J24</f>
+      <c r="J26" s="8">
+        <f t="shared" ref="J26:P26" si="15">+J24-J25</f>
         <v>-1135</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K26" s="8">
         <f t="shared" si="15"/>
         <v>31650</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L26" s="8">
         <f t="shared" si="15"/>
         <v>21958</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M26" s="8">
         <f t="shared" si="15"/>
         <v>32709</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N26" s="8">
         <f t="shared" si="15"/>
         <v>12406</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O26" s="8">
         <f t="shared" si="15"/>
         <v>46571</v>
       </c>
-      <c r="X25" s="8">
-        <f>+X23-X24</f>
+      <c r="P26" s="8">
+        <f t="shared" si="15"/>
+        <v>35602</v>
+      </c>
+      <c r="X26" s="8">
+        <f>+X24-X25</f>
         <v>35276</v>
       </c>
-      <c r="Y25" s="8">
-        <f>+Y23-Y24</f>
+      <c r="Y26" s="8">
+        <f>+Y24-Y25</f>
         <v>63808</v>
       </c>
-      <c r="Z25" s="8">
-        <f>+Z23-Z24</f>
+      <c r="Z26" s="8">
+        <f>+Z24-Z25</f>
         <v>98723</v>
       </c>
-    </row>
-    <row r="26" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:70" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="12">
-        <f t="shared" ref="C27:H27" si="16">+C25/C28</f>
+      <c r="C28" s="12">
+        <f t="shared" ref="C28:H28" si="16">+C26/C29</f>
         <v>22.262139298476221</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D28" s="12">
         <f t="shared" si="16"/>
         <v>-174.00271459792663</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E28" s="12">
         <f t="shared" si="16"/>
         <v>-340.87626624938014</v>
       </c>
-      <c r="F27" s="12" t="e">
+      <c r="F28" s="12">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G27" s="12">
+        <v>548.36841234373048</v>
+      </c>
+      <c r="G28" s="12">
         <f t="shared" si="16"/>
         <v>36.654522788407427</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H28" s="12">
         <f t="shared" si="16"/>
         <v>21.298860831508435</v>
       </c>
-      <c r="I27" s="12">
-        <f>+I25/I28</f>
+      <c r="I28" s="12">
+        <f>+I26/I29</f>
         <v>31.354480047458221</v>
       </c>
-      <c r="J27" s="12">
-        <f t="shared" ref="J27:O27" si="17">+J25/J28</f>
+      <c r="J28" s="12">
+        <f t="shared" ref="J28:P28" si="17">+J26/J29</f>
         <v>-1.5611804944298882</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K28" s="12">
         <f t="shared" si="17"/>
         <v>44.26723755635679</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L28" s="12">
         <f t="shared" si="17"/>
         <v>30.720007084264751</v>
       </c>
-      <c r="M27" s="12">
+      <c r="M28" s="12">
         <f t="shared" si="17"/>
         <v>45.724263250456808</v>
       </c>
-      <c r="N27" s="12">
+      <c r="N28" s="12">
         <f t="shared" si="17"/>
         <v>17.35840682767957</v>
       </c>
-      <c r="O27" s="12">
+      <c r="O28" s="12">
         <f t="shared" si="17"/>
         <v>65.712791315061338</v>
       </c>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="Y27" s="8">
-        <f>+Y25/Y28</f>
+      <c r="P28" s="12">
+        <f t="shared" si="17"/>
+        <v>50.228979147184361</v>
+      </c>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="Y28" s="8">
+        <f>+Y26/Y29</f>
         <v>88.301123892658509</v>
       </c>
-      <c r="Z27" s="8">
-        <f>+Z25/Z28</f>
+      <c r="Z28" s="8">
+        <f>+Z26/Z29</f>
         <v>138.13267751483235</v>
       </c>
     </row>
-    <row r="28" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
+    <row r="29" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C29" s="6">
         <f>183.169728*4</f>
         <v>732.67891199999997</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D29" s="6">
         <v>732.74718900000005</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E29" s="6">
         <v>732.80549199999996</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6">
+      <c r="F29" s="3">
+        <v>722.61820899999998</v>
+      </c>
+      <c r="G29" s="6">
         <f>182.378585*4</f>
         <v>729.51433999999995</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H29" s="6">
         <v>726.84638500000005</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I29" s="6">
         <v>724.68112900000006</v>
       </c>
-      <c r="J28" s="6">
-        <f>+AVERAGE(G28:I28)</f>
+      <c r="J29" s="6">
+        <f>+AVERAGE(G29:I29)</f>
         <v>727.01395133333335</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K29" s="6">
         <v>714.97571900000003</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L29" s="6">
         <v>714.77848100000006</v>
       </c>
-      <c r="M28" s="3">
+      <c r="M29" s="3">
         <v>715.35324300000002</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N29" s="3">
         <v>714.69692599999996</v>
       </c>
-      <c r="O28" s="3">
+      <c r="O29" s="3">
         <v>708.70524699999999</v>
       </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3">
-        <v>722.61820899999998</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>714.69692599999996</v>
-      </c>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="3"/>
-      <c r="AG28" s="3"/>
-      <c r="AH28" s="3"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="3"/>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
-      <c r="AM28" s="3"/>
-      <c r="AN28" s="3"/>
-      <c r="AO28" s="3"/>
-      <c r="AP28" s="3"/>
-      <c r="AQ28" s="3"/>
-      <c r="AR28" s="3"/>
-      <c r="AS28" s="3"/>
-      <c r="AT28" s="3"/>
-      <c r="AU28" s="3"/>
-      <c r="AV28" s="3"/>
-      <c r="AW28" s="3"/>
-      <c r="AX28" s="3"/>
-      <c r="AY28" s="3"/>
-      <c r="AZ28" s="3"/>
-      <c r="BA28" s="3"/>
-      <c r="BB28" s="3"/>
-      <c r="BC28" s="6"/>
-      <c r="BD28" s="6"/>
-      <c r="BE28" s="6"/>
-      <c r="BF28" s="6"/>
-      <c r="BG28" s="6"/>
-      <c r="BH28" s="3"/>
-      <c r="BI28" s="3"/>
-      <c r="BJ28" s="3"/>
-      <c r="BK28" s="3"/>
-      <c r="BL28" s="3"/>
-      <c r="BM28" s="3"/>
-      <c r="BN28" s="3"/>
-      <c r="BO28" s="3"/>
-      <c r="BP28" s="3"/>
-      <c r="BQ28" s="3"/>
-      <c r="BR28" s="3"/>
-    </row>
-    <row r="29" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3">
+        <v>708.79401900000005</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -2471,8 +2517,12 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
+      <c r="Y29" s="3">
+        <v>722.61820899999998</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>714.69692599999996</v>
+      </c>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -2519,52 +2569,22 @@
       <c r="BR29" s="3"/>
     </row>
     <row r="30" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="9">
-        <f t="shared" ref="G30:G35" si="18">+G6/C6-1</f>
-        <v>0.12810442416541523</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" ref="H30:H35" si="19">+H6/D6-1</f>
-        <v>0.18709778909132502</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" ref="I30:J34" si="20">+I6/E6-1</f>
-        <v>0.10277542880943069</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" si="20"/>
-        <v>0.16649960074075332</v>
-      </c>
-      <c r="K30" s="9">
-        <f t="shared" ref="K30:K35" si="21">+K6/G6-1</f>
-        <v>0.11501353903565659</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" ref="L30:O35" si="22">+L6/H6-1</f>
-        <v>4.7609295377609717E-2</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.1369629409206401</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.15406574520456173</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.19121863616419899</v>
-      </c>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -2620,49 +2640,52 @@
     </row>
     <row r="31" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="9">
-        <f t="shared" si="18"/>
-        <v>9.4235082010465598E-2</v>
+        <f>+G6/C6-1</f>
+        <v>0.12810442416541523</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="19"/>
-        <v>-2.7531234100288349E-2</v>
+        <f>+H6/D6-1</f>
+        <v>0.18709778909132502</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="20"/>
-        <v>0.10573285478707928</v>
+        <f>+I6/E6-1</f>
+        <v>0.10277542880943069</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="20"/>
-        <v>0.23680893210877008</v>
+        <f>+J6/F6-1</f>
+        <v>0.16649960074075332</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="21"/>
-        <v>2.463430316669335E-2</v>
+        <f>+K6/G6-1</f>
+        <v>0.11501353903565659</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="22"/>
-        <v>8.2490408092082301E-2</v>
+        <f>+L6/H6-1</f>
+        <v>4.7609295377609717E-2</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="22"/>
-        <v>0.11799280638652521</v>
+        <f>+M6/I6-1</f>
+        <v>0.1369629409206401</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="22"/>
-        <v>0.19605416423995337</v>
+        <f>+N6/J6-1</f>
+        <v>0.15406574520456173</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="22"/>
-        <v>0.19821939836059155</v>
-      </c>
-      <c r="P31" s="9"/>
+        <f>+O6/K6-1</f>
+        <v>0.19121863616419899</v>
+      </c>
+      <c r="P31" s="9">
+        <f>+P6/L6-1</f>
+        <v>0.19489196306390211</v>
+      </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="3"/>
@@ -2720,49 +2743,52 @@
     </row>
     <row r="32" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="9">
-        <f t="shared" si="18"/>
-        <v>-2.9151483602290473E-2</v>
+        <f>+G7/C7-1</f>
+        <v>9.4235082010465598E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="19"/>
-        <v>0.10838252656434477</v>
+        <f>+H7/D7-1</f>
+        <v>-2.7531234100288349E-2</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="20"/>
-        <v>4.7671728854470574E-2</v>
+        <f>+I7/E7-1</f>
+        <v>0.10573285478707928</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="20"/>
-        <v>9.4036978082527201E-2</v>
+        <f>+J7/F7-1</f>
+        <v>0.23680893210877008</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="21"/>
-        <v>0.10873994638069706</v>
+        <f>+K7/G7-1</f>
+        <v>2.463430316669335E-2</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="22"/>
-        <v>2.9399233063485353E-2</v>
+        <f>+L7/H7-1</f>
+        <v>8.2490408092082301E-2</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="22"/>
-        <v>0.17500239992320243</v>
+        <f>+M7/I7-1</f>
+        <v>0.11799280638652521</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="22"/>
-        <v>9.9944040290990577E-2</v>
+        <f>+N7/J7-1</f>
+        <v>0.19605416423995337</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="22"/>
-        <v>0.39529935196827548</v>
-      </c>
-      <c r="P32" s="9"/>
+        <f>+O7/K7-1</f>
+        <v>0.19821939836059155</v>
+      </c>
+      <c r="P32" s="9">
+        <f>+P7/L7-1</f>
+        <v>0.31894098061328613</v>
+      </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="3"/>
@@ -2820,49 +2846,52 @@
     </row>
     <row r="33" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="9">
-        <f t="shared" si="18"/>
-        <v>0.51694969974817595</v>
+        <f>+G8/C8-1</f>
+        <v>-2.9151483602290473E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="19"/>
-        <v>0.7865766481334393</v>
+        <f>+H8/D8-1</f>
+        <v>0.10838252656434477</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="20"/>
-        <v>0.62736983390190715</v>
+        <f>+I8/E8-1</f>
+        <v>4.7671728854470574E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="20"/>
-        <v>0.75501917437401311</v>
+        <f>+J8/F8-1</f>
+        <v>9.4036978082527201E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="21"/>
-        <v>0.49593495934959342</v>
+        <f>+K8/G8-1</f>
+        <v>0.10873994638069706</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="22"/>
-        <v>0.43022273596229943</v>
+        <f>+L8/H8-1</f>
+        <v>2.9399233063485353E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="22"/>
-        <v>0.43406989930925466</v>
+        <f>+M8/I8-1</f>
+        <v>0.17500239992320243</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="22"/>
-        <v>0.38303341902313615</v>
+        <f>+N8/J8-1</f>
+        <v>9.9944040290990577E-2</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="22"/>
-        <v>0.69647735033007052</v>
-      </c>
-      <c r="P33" s="9"/>
+        <f>+O8/K8-1</f>
+        <v>0.39529935196827548</v>
+      </c>
+      <c r="P33" s="9">
+        <f>+P8/L8-1</f>
+        <v>0.15925082781456945</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="3"/>
@@ -2920,49 +2949,52 @@
     </row>
     <row r="34" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="9">
-        <f t="shared" si="18"/>
-        <v>0.48663807324315411</v>
+        <f>+G9/C9-1</f>
+        <v>0.51694969974817595</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="19"/>
-        <v>0.59896123168243376</v>
+        <f>+H9/D9-1</f>
+        <v>0.7865766481334393</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="20"/>
-        <v>0.48706038487060388</v>
+        <f>+I9/E9-1</f>
+        <v>0.62736983390190715</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="20"/>
-        <v>0.74361633182112774</v>
+        <f>+J9/F9-1</f>
+        <v>0.75501917437401311</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="21"/>
-        <v>0.57151575676875277</v>
+        <f>+K9/G9-1</f>
+        <v>0.49593495934959342</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="22"/>
-        <v>0.4520881670533643</v>
+        <f>+L9/H9-1</f>
+        <v>0.43022273596229943</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="22"/>
-        <v>0.37925439130258409</v>
+        <f>+M9/I9-1</f>
+        <v>0.43406989930925466</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="22"/>
-        <v>0.36199078203984536</v>
+        <f>+N9/J9-1</f>
+        <v>0.38303341902313615</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="22"/>
-        <v>0.33772285966460713</v>
-      </c>
-      <c r="P34" s="9"/>
+        <f>+O9/K9-1</f>
+        <v>0.69647735033007052</v>
+      </c>
+      <c r="P34" s="9">
+        <f>+P9/L9-1</f>
+        <v>0.97590923220391668</v>
+      </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="3"/>
@@ -3019,75 +3051,63 @@
       <c r="BR34" s="3"/>
     </row>
     <row r="35" spans="2:70" x14ac:dyDescent="0.2">
-      <c r="B35" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="10">
-        <f t="shared" si="18"/>
-        <v>0.14317419253169783</v>
-      </c>
-      <c r="H35" s="10">
-        <f t="shared" si="19"/>
-        <v>0.22002148321261128</v>
-      </c>
-      <c r="I35" s="10">
-        <f>+I11/E11-1</f>
-        <v>0.15965094351562392</v>
-      </c>
-      <c r="J35" s="10">
-        <f>+J11/F11-1</f>
-        <v>0.25101750600696326</v>
-      </c>
-      <c r="K35" s="10">
-        <f t="shared" si="21"/>
-        <v>0.19649975301834566</v>
-      </c>
-      <c r="L35" s="10">
-        <f t="shared" si="22"/>
-        <v>0.1569807908529004</v>
-      </c>
-      <c r="M35" s="10">
-        <f t="shared" si="22"/>
-        <v>0.21282911789582815</v>
-      </c>
-      <c r="N35" s="10">
-        <f t="shared" si="22"/>
-        <v>0.21420638653705448</v>
-      </c>
-      <c r="O35" s="10">
-        <f t="shared" si="22"/>
-        <v>0.29739862610590784</v>
-      </c>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
+      <c r="B35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="9">
+        <f>+G10/C10-1</f>
+        <v>0.48663807324315411</v>
+      </c>
+      <c r="H35" s="9">
+        <f>+H10/D10-1</f>
+        <v>0.59896123168243376</v>
+      </c>
+      <c r="I35" s="9">
+        <f>+I10/E10-1</f>
+        <v>0.48706038487060388</v>
+      </c>
+      <c r="J35" s="9">
+        <f>+J10/F10-1</f>
+        <v>0.74361633182112774</v>
+      </c>
+      <c r="K35" s="9">
+        <f>+K10/G10-1</f>
+        <v>0.57151575676875277</v>
+      </c>
+      <c r="L35" s="9">
+        <f>+L10/H10-1</f>
+        <v>0.4520881670533643</v>
+      </c>
+      <c r="M35" s="9">
+        <f>+M10/I10-1</f>
+        <v>0.37925439130258409</v>
+      </c>
+      <c r="N35" s="9">
+        <f>+N10/J10-1</f>
+        <v>0.36199078203984536</v>
+      </c>
+      <c r="O35" s="9">
+        <f>+O10/K10-1</f>
+        <v>0.33772285966460713</v>
+      </c>
+      <c r="P35" s="9">
+        <f>+P10/L10-1</f>
+        <v>0.37524966046177188</v>
+      </c>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
-      <c r="V35" s="10" t="e">
-        <f t="shared" ref="V35:X35" si="23">+V11/U11-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W35" s="10">
-        <f t="shared" si="23"/>
-        <v>0.19926104290455182</v>
-      </c>
-      <c r="X35" s="10">
-        <f t="shared" si="23"/>
-        <v>0.17718081473211988</v>
-      </c>
-      <c r="Y35" s="10">
-        <f>+Y11/X11-1</f>
-        <v>0.18943033991687463</v>
-      </c>
-      <c r="Z35" s="10">
-        <f t="shared" ref="Z35" si="24">+Z11/Y11-1</f>
-        <v>0.19511411500812059</v>
-      </c>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -3134,92 +3154,77 @@
       <c r="BR35" s="3"/>
     </row>
     <row r="36" spans="2:70" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="9">
-        <f t="shared" ref="C36:H36" si="25">+C13/C11</f>
-        <v>0.50180896537686237</v>
-      </c>
-      <c r="D36" s="9">
-        <f t="shared" si="25"/>
-        <v>-3.1215978865163811E-2</v>
-      </c>
-      <c r="E36" s="9">
-        <f t="shared" si="25"/>
-        <v>-0.38253831647956665</v>
-      </c>
-      <c r="F36" s="9">
-        <f t="shared" si="25"/>
-        <v>2.3310694846270779</v>
-      </c>
-      <c r="G36" s="9">
-        <f t="shared" si="25"/>
-        <v>0.54478409208395073</v>
-      </c>
-      <c r="H36" s="9">
-        <f t="shared" si="25"/>
-        <v>0.56659547761114115</v>
-      </c>
-      <c r="I36" s="9">
-        <f>+I13/I11</f>
-        <v>0.55021691086191371</v>
-      </c>
-      <c r="J36" s="9">
-        <f>+J13/J11</f>
-        <v>0.57461194731890874</v>
-      </c>
-      <c r="K36" s="9">
-        <f t="shared" ref="K36:L36" si="26">+K13/K11</f>
-        <v>0.55840490031827106</v>
-      </c>
-      <c r="L36" s="9">
-        <f t="shared" si="26"/>
-        <v>0.57649176028999671</v>
-      </c>
-      <c r="M36" s="9">
-        <f t="shared" ref="M36:N36" si="27">+M13/M11</f>
-        <v>0.5612016719383417</v>
-      </c>
-      <c r="N36" s="9">
-        <f t="shared" si="27"/>
-        <v>0.57817401176147765</v>
-      </c>
-      <c r="O36" s="9">
-        <f t="shared" ref="O36" si="28">+O13/O11</f>
-        <v>0.54583094370340224</v>
-      </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
+      <c r="B36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="10">
+        <f t="shared" ref="G36" si="18">+G12/C12-1</f>
+        <v>0.14317419253169783</v>
+      </c>
+      <c r="H36" s="10">
+        <f t="shared" ref="H36" si="19">+H12/D12-1</f>
+        <v>0.22002148321261128</v>
+      </c>
+      <c r="I36" s="10">
+        <f>+I12/E12-1</f>
+        <v>0.15965094351562392</v>
+      </c>
+      <c r="J36" s="10">
+        <f>+J12/F12-1</f>
+        <v>0.25101750600696326</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" ref="K36" si="20">+K12/G12-1</f>
+        <v>0.19649975301834566</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" ref="L36:P36" si="21">+L12/H12-1</f>
+        <v>0.1569807908529004</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="21"/>
+        <v>0.21282911789582815</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="21"/>
+        <v>0.21420638653705448</v>
+      </c>
+      <c r="O36" s="10">
+        <f t="shared" si="21"/>
+        <v>0.29739862610590784</v>
+      </c>
+      <c r="P36" s="10">
+        <f t="shared" si="21"/>
+        <v>0.35855207342468565</v>
+      </c>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
       <c r="S36" s="3"/>
-      <c r="T36" s="9" t="e">
-        <f t="shared" ref="T36:X36" si="29">+T13/T11</f>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="10" t="e">
+        <f t="shared" ref="V36:X36" si="22">+V12/U12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U36" s="9" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V36" s="9">
-        <f t="shared" si="29"/>
-        <v>0.49464590195578634</v>
-      </c>
-      <c r="W36" s="9">
-        <f t="shared" si="29"/>
-        <v>0.49671172779255512</v>
-      </c>
-      <c r="X36" s="9">
-        <f t="shared" si="29"/>
-        <v>0.52044917900021559</v>
-      </c>
-      <c r="Y36" s="9">
-        <f>+Y13/Y11</f>
-        <v>0.55838390864904219</v>
-      </c>
-      <c r="Z36" s="9">
-        <f t="shared" ref="Z36" si="30">+Z13/Z11</f>
-        <v>0.56804033956661359</v>
+      <c r="W36" s="10">
+        <f t="shared" si="22"/>
+        <v>0.19926104290455182</v>
+      </c>
+      <c r="X36" s="10">
+        <f t="shared" si="22"/>
+        <v>0.17718081473211988</v>
+      </c>
+      <c r="Y36" s="10">
+        <f>+Y12/X12-1</f>
+        <v>0.18943033991687463</v>
+      </c>
+      <c r="Z36" s="10">
+        <f t="shared" ref="Z36" si="23">+Z12/Y12-1</f>
+        <v>0.19511411500812059</v>
       </c>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
@@ -3268,91 +3273,94 @@
     </row>
     <row r="37" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:H37" si="31">+C15/C11</f>
-        <v>0.1452490856681353</v>
+        <f t="shared" ref="C37:H37" si="24">+C14/C12</f>
+        <v>0.50180896537686237</v>
       </c>
       <c r="D37" s="9">
-        <f t="shared" si="31"/>
-        <v>-0.86140424728919596</v>
+        <f t="shared" si="24"/>
+        <v>-3.1215978865163811E-2</v>
       </c>
       <c r="E37" s="9">
-        <f t="shared" si="31"/>
-        <v>-1.4824965512004353</v>
+        <f t="shared" si="24"/>
+        <v>-0.38253831647956665</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" si="31"/>
-        <v>3.1469540201703197</v>
+        <f t="shared" si="24"/>
+        <v>2.3310694846270779</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="31"/>
-        <v>0.19421948053439939</v>
+        <f t="shared" si="24"/>
+        <v>0.54478409208395073</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="31"/>
-        <v>0.1498123107491508</v>
+        <f t="shared" si="24"/>
+        <v>0.56659547761114115</v>
       </c>
       <c r="I37" s="9">
-        <f>+I15/I11</f>
-        <v>0.17749583913126518</v>
+        <f>+I14/I12</f>
+        <v>0.55021691086191371</v>
       </c>
       <c r="J37" s="9">
-        <f>+J15/J11</f>
-        <v>5.6104316922755304E-2</v>
+        <f>+J14/J12</f>
+        <v>0.57461194731890874</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" ref="K37:L37" si="32">+K15/K11</f>
-        <v>0.21368325548573541</v>
+        <f t="shared" ref="K37:L37" si="25">+K14/K12</f>
+        <v>0.55840490031827106</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="32"/>
-        <v>0.18828701442270612</v>
+        <f t="shared" si="25"/>
+        <v>0.57649176028999671</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" ref="M37:N37" si="33">+M15/M11</f>
-        <v>0.20910477510269643</v>
+        <f t="shared" ref="M37:N37" si="26">+M14/M12</f>
+        <v>0.5612016719383417</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="33"/>
-        <v>8.0242762064123188E-2</v>
+        <f t="shared" si="26"/>
+        <v>0.57817401176147765</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" ref="O37" si="34">+O15/O11</f>
-        <v>0.22483118420809206</v>
-      </c>
-      <c r="P37" s="9"/>
+        <f t="shared" ref="O37:P37" si="27">+O14/O12</f>
+        <v>0.54583094370340224</v>
+      </c>
+      <c r="P37" s="9">
+        <f t="shared" si="27"/>
+        <v>0.60087503500896988</v>
+      </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="3"/>
       <c r="T37" s="9" t="e">
-        <f t="shared" ref="T37:Z37" si="35">+T15/T11</f>
+        <f t="shared" ref="T37:X37" si="28">+T14/T12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U37" s="9" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V37" s="9">
-        <f t="shared" si="35"/>
-        <v>5.4310624302432914E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.49464590195578634</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" si="35"/>
-        <v>7.0167003369782557E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.49671172779255512</v>
       </c>
       <c r="X37" s="9">
-        <f t="shared" si="35"/>
-        <v>9.5040344421987055E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.52044917900021559</v>
       </c>
       <c r="Y37" s="9">
-        <f t="shared" si="35"/>
-        <v>0.14754335132330965</v>
+        <f>+Y14/Y12</f>
+        <v>0.55838390864904219</v>
       </c>
       <c r="Z37" s="9">
-        <f t="shared" si="35"/>
-        <v>0.17575309896462765</v>
+        <f t="shared" ref="Z37" si="29">+Z14/Z12</f>
+        <v>0.56804033956661359</v>
       </c>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
@@ -3401,91 +3409,94 @@
     </row>
     <row r="38" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C38" s="9">
-        <f t="shared" ref="C38:H38" si="36">+C22/C21</f>
-        <v>0.24017588521175653</v>
+        <f t="shared" ref="C38:H38" si="30">+C16/C12</f>
+        <v>0.1452490856681353</v>
       </c>
       <c r="D38" s="9">
-        <f t="shared" si="36"/>
-        <v>-7.1262763040589414E-2</v>
+        <f t="shared" si="30"/>
+        <v>-0.86140424728919596</v>
       </c>
       <c r="E38" s="9">
-        <f t="shared" si="36"/>
-        <v>-6.3295720672769853E-2</v>
+        <f t="shared" si="30"/>
+        <v>-1.4824965512004353</v>
       </c>
       <c r="F38" s="9">
-        <f t="shared" si="36"/>
-        <v>-3.5033627893122352E-2</v>
+        <f t="shared" si="30"/>
+        <v>3.1469540201703197</v>
       </c>
       <c r="G38" s="9">
-        <f t="shared" si="36"/>
-        <v>0.1886946527945802</v>
+        <f t="shared" si="30"/>
+        <v>0.19421948053439939</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="36"/>
-        <v>0.38095619123824764</v>
+        <f t="shared" si="30"/>
+        <v>0.1498123107491508</v>
       </c>
       <c r="I38" s="9">
-        <f>+I22/I21</f>
-        <v>0.33369590780809033</v>
+        <f>+I16/I12</f>
+        <v>0.17749583913126518</v>
       </c>
       <c r="J38" s="9">
-        <f>+J22/J21</f>
-        <v>1.8692307692307693</v>
+        <f>+J16/J12</f>
+        <v>5.6104316922755304E-2</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" ref="K38:L38" si="37">+K22/K21</f>
-        <v>0.26862437765074682</v>
+        <f t="shared" ref="K38:L38" si="31">+K16/K12</f>
+        <v>0.21368325548573541</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="37"/>
-        <v>0.41217735889471996</v>
+        <f t="shared" si="31"/>
+        <v>0.18828701442270612</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:N38" si="38">+M22/M21</f>
-        <v>0.28637544480101296</v>
+        <f t="shared" ref="M38:N38" si="32">+M16/M12</f>
+        <v>0.20910477510269643</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="38"/>
-        <v>-2.0144120537176548E-2</v>
+        <f t="shared" si="32"/>
+        <v>8.0242762064123188E-2</v>
       </c>
       <c r="O38" s="9">
-        <f t="shared" ref="O38" si="39">+O22/O21</f>
-        <v>0.24564409245191532</v>
-      </c>
-      <c r="P38" s="9"/>
+        <f t="shared" ref="O38:P38" si="33">+O16/O12</f>
+        <v>0.22483118420809206</v>
+      </c>
+      <c r="P38" s="9">
+        <f t="shared" si="33"/>
+        <v>0.22603683322105231</v>
+      </c>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="3"/>
       <c r="T38" s="9" t="e">
-        <f t="shared" ref="T38:Z38" si="40">+T22/T21</f>
+        <f t="shared" ref="T38:Z38" si="34">+T16/T12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U38" s="9" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V38" s="9" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W38" s="9" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
+      <c r="V38" s="9">
+        <f t="shared" si="34"/>
+        <v>5.4310624302432914E-2</v>
+      </c>
+      <c r="W38" s="9">
+        <f t="shared" si="34"/>
+        <v>7.0167003369782557E-2</v>
       </c>
       <c r="X38" s="9">
-        <f t="shared" si="40"/>
-        <v>0.29894216510133464</v>
+        <f t="shared" si="34"/>
+        <v>9.5040344421987055E-2</v>
       </c>
       <c r="Y38" s="9">
-        <f t="shared" si="40"/>
-        <v>0.31421523942302537</v>
+        <f t="shared" si="34"/>
+        <v>0.14754335132330965</v>
       </c>
       <c r="Z38" s="9">
-        <f t="shared" si="40"/>
-        <v>0.28770963812873418</v>
+        <f t="shared" si="34"/>
+        <v>0.17575309896462765</v>
       </c>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
@@ -3533,30 +3544,96 @@
       <c r="BR38" s="3"/>
     </row>
     <row r="39" spans="2:70" x14ac:dyDescent="0.2">
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
+      <c r="B39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="9">
+        <f t="shared" ref="C39:H39" si="35">+C23/C22</f>
+        <v>0.24017588521175653</v>
+      </c>
+      <c r="D39" s="9">
+        <f t="shared" si="35"/>
+        <v>-7.1262763040589414E-2</v>
+      </c>
+      <c r="E39" s="9">
+        <f t="shared" si="35"/>
+        <v>-6.3295720672769853E-2</v>
+      </c>
+      <c r="F39" s="9">
+        <f t="shared" si="35"/>
+        <v>-3.5033627893122352E-2</v>
+      </c>
+      <c r="G39" s="9">
+        <f t="shared" si="35"/>
+        <v>0.1886946527945802</v>
+      </c>
+      <c r="H39" s="9">
+        <f t="shared" si="35"/>
+        <v>0.38095619123824764</v>
+      </c>
+      <c r="I39" s="9">
+        <f>+I23/I22</f>
+        <v>0.33369590780809033</v>
+      </c>
+      <c r="J39" s="9">
+        <f>+J23/J22</f>
+        <v>1.8692307692307693</v>
+      </c>
+      <c r="K39" s="9">
+        <f t="shared" ref="K39:L39" si="36">+K23/K22</f>
+        <v>0.26862437765074682</v>
+      </c>
+      <c r="L39" s="9">
+        <f t="shared" si="36"/>
+        <v>0.41217735889471996</v>
+      </c>
+      <c r="M39" s="9">
+        <f t="shared" ref="M39:N39" si="37">+M23/M22</f>
+        <v>0.28637544480101296</v>
+      </c>
+      <c r="N39" s="9">
+        <f t="shared" si="37"/>
+        <v>-2.0144120537176548E-2</v>
+      </c>
+      <c r="O39" s="9">
+        <f t="shared" ref="O39:P39" si="38">+O23/O22</f>
+        <v>0.24564409245191532</v>
+      </c>
+      <c r="P39" s="9">
+        <f t="shared" si="38"/>
+        <v>0.28513765889511417</v>
+      </c>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
       <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
+      <c r="T39" s="9" t="e">
+        <f t="shared" ref="T39:Z39" si="39">+T23/T22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U39" s="9" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V39" s="9" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W39" s="9" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X39" s="9">
+        <f t="shared" si="39"/>
+        <v>0.29894216510133464</v>
+      </c>
+      <c r="Y39" s="9">
+        <f t="shared" si="39"/>
+        <v>0.31421523942302537</v>
+      </c>
+      <c r="Z39" s="9">
+        <f t="shared" si="39"/>
+        <v>0.28770963812873418</v>
+      </c>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
@@ -10795,11 +10872,11 @@
       <c r="AZ142" s="3"/>
       <c r="BA142" s="3"/>
       <c r="BB142" s="3"/>
-      <c r="BC142" s="3"/>
-      <c r="BD142" s="3"/>
-      <c r="BE142" s="3"/>
-      <c r="BF142" s="3"/>
-      <c r="BG142" s="3"/>
+      <c r="BC142" s="6"/>
+      <c r="BD142" s="6"/>
+      <c r="BE142" s="6"/>
+      <c r="BF142" s="6"/>
+      <c r="BG142" s="6"/>
       <c r="BH142" s="3"/>
       <c r="BI142" s="3"/>
       <c r="BJ142" s="3"/>
@@ -23132,6 +23209,76 @@
       <c r="BQ318" s="3"/>
       <c r="BR318" s="3"/>
     </row>
+    <row r="319" spans="3:70" x14ac:dyDescent="0.2">
+      <c r="C319" s="3"/>
+      <c r="D319" s="3"/>
+      <c r="E319" s="3"/>
+      <c r="F319" s="3"/>
+      <c r="G319" s="3"/>
+      <c r="H319" s="3"/>
+      <c r="I319" s="3"/>
+      <c r="J319" s="3"/>
+      <c r="K319" s="3"/>
+      <c r="L319" s="3"/>
+      <c r="M319" s="3"/>
+      <c r="N319" s="3"/>
+      <c r="O319" s="3"/>
+      <c r="P319" s="3"/>
+      <c r="Q319" s="3"/>
+      <c r="R319" s="3"/>
+      <c r="S319" s="3"/>
+      <c r="T319" s="3"/>
+      <c r="U319" s="3"/>
+      <c r="V319" s="3"/>
+      <c r="W319" s="3"/>
+      <c r="X319" s="3"/>
+      <c r="Y319" s="3"/>
+      <c r="Z319" s="3"/>
+      <c r="AA319" s="3"/>
+      <c r="AB319" s="3"/>
+      <c r="AC319" s="3"/>
+      <c r="AD319" s="3"/>
+      <c r="AE319" s="3"/>
+      <c r="AF319" s="3"/>
+      <c r="AG319" s="3"/>
+      <c r="AH319" s="3"/>
+      <c r="AI319" s="3"/>
+      <c r="AJ319" s="3"/>
+      <c r="AK319" s="3"/>
+      <c r="AL319" s="3"/>
+      <c r="AM319" s="3"/>
+      <c r="AN319" s="3"/>
+      <c r="AO319" s="3"/>
+      <c r="AP319" s="3"/>
+      <c r="AQ319" s="3"/>
+      <c r="AR319" s="3"/>
+      <c r="AS319" s="3"/>
+      <c r="AT319" s="3"/>
+      <c r="AU319" s="3"/>
+      <c r="AV319" s="3"/>
+      <c r="AW319" s="3"/>
+      <c r="AX319" s="3"/>
+      <c r="AY319" s="3"/>
+      <c r="AZ319" s="3"/>
+      <c r="BA319" s="3"/>
+      <c r="BB319" s="3"/>
+      <c r="BC319" s="3"/>
+      <c r="BD319" s="3"/>
+      <c r="BE319" s="3"/>
+      <c r="BF319" s="3"/>
+      <c r="BG319" s="3"/>
+      <c r="BH319" s="3"/>
+      <c r="BI319" s="3"/>
+      <c r="BJ319" s="3"/>
+      <c r="BK319" s="3"/>
+      <c r="BL319" s="3"/>
+      <c r="BM319" s="3"/>
+      <c r="BN319" s="3"/>
+      <c r="BO319" s="3"/>
+      <c r="BP319" s="3"/>
+      <c r="BQ319" s="3"/>
+      <c r="BR319" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C74D512B-33C6-4D7F-AAEB-7048EF7D73C1}"/>
